--- a/SpringClassics/SpringClassics.xlsx
+++ b/SpringClassics/SpringClassics.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ride the White Roads race 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ride the White Roads race 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Primavera race 1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1789,7 +1790,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3009,6 +3010,663 @@
       </c>
       <c r="I39" t="n">
         <v>2.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>avg_power</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>avg_wkg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>182292</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JOHAN GREN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>eSRT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01:15:14.388</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>328</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1417072</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kelvin Newman</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>teamWKG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01:16:14.454</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>60.066</v>
+      </c>
+      <c r="H3" t="n">
+        <v>246</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1175748</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jos Castelijns(TeamNL)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TeamNL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01:16:14.679</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>60.291</v>
+      </c>
+      <c r="H4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3102903</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&amp;#321;ukasz Dul</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>T175</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01:17:07.587</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>113.199</v>
+      </c>
+      <c r="H5" t="n">
+        <v>284</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1593779</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Alberto Goldoni (TSE)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01:21:22.240</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>367.852</v>
+      </c>
+      <c r="H6" t="n">
+        <v>291</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1387591</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tommy Sellars (TFC Typhoon)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TFC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>01:23:31.337</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>496.949</v>
+      </c>
+      <c r="H7" t="n">
+        <v>296</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3640893</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Christian Strauch</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01:23:54.202</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>519.814</v>
+      </c>
+      <c r="H8" t="n">
+        <v>253</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3353670</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wim Van Cutsem [BikeRepublic]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BikeRepublic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>01:23:56.168</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>247</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1948296</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jorge Sanchis </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01:28:21.240</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>221</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8086912</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R G Cycling  (Diabetic Cyclist) </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01:29:59.274</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>98.03400000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>181</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6345533</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mark Tighe</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INOX</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>01:36:40.454</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>499.214</v>
+      </c>
+      <c r="H12" t="n">
+        <v>195</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6411187</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ken Wahid</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>01:32:47.373</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>202</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6147623</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>John Moulding</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>01:36:40.302</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>232.929</v>
+      </c>
+      <c r="H14" t="n">
+        <v>207</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>229572</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabio Bevilacqua (TDRS) </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>01:36:51.461</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>244.088</v>
+      </c>
+      <c r="H15" t="n">
+        <v>177</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3622652</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Francky Lootvoet</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>01:37:22.310</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>274.937</v>
+      </c>
+      <c r="H16" t="n">
+        <v>187</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7669986</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ren&amp;eacute; Servais</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>01:43:24.788</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>183</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/SpringClassics/SpringClassics.xlsx
+++ b/SpringClassics/SpringClassics.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ride the White Roads race 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ride the White Roads race 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Primavera race 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Primavera race 2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3672,4 +3673,708 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>avg_power</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>avg_wkg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>856836</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nicklas Bekker #SISU#</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SISU Racing</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01:15:19.846</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>293</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1255437</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Philip Caldwell</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01:16:48.876</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="H3" t="n">
+        <v>305</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>640691</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Travis Samuel </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wahoo Esports</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01:18:15.079</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>175.233</v>
+      </c>
+      <c r="H4" t="n">
+        <v>261</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2505644</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>J Z CancelCancer.ai</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01:18:19.375</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>179.529</v>
+      </c>
+      <c r="H5" t="n">
+        <v>263</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>71087</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A Max</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01:18:19.800</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>179.954</v>
+      </c>
+      <c r="H6" t="n">
+        <v>254</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5893609</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Aled Jones</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>01:18:19.984</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>180.138</v>
+      </c>
+      <c r="H7" t="n">
+        <v>282</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50641</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Eric Sorenson [DRAFT]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[DRAFT]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01:18:21.042</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>181.196</v>
+      </c>
+      <c r="H8" t="n">
+        <v>257</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5639510</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kasper s&amp;oslash;rensen</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>eCKD/SeC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>01:18:21.609</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>181.763</v>
+      </c>
+      <c r="H9" t="n">
+        <v>277</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6778481</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Giovanni Bettega</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INOX</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01:20:23.764</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>303.918</v>
+      </c>
+      <c r="H10" t="n">
+        <v>262</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6070919</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-Valentin Escalona</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01:23:17.850</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>478.004</v>
+      </c>
+      <c r="H11" t="n">
+        <v>271</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>91113</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Patrick Tremblay</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rouleurs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>01:20:22.801</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>268</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7004523</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>trevor barnes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5.W.4.T</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>01:24:32.830</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>250.029</v>
+      </c>
+      <c r="H13" t="n">
+        <v>277</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1075425</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rok Be&amp;scaron;ter  </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SLOVENIA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>01:25:49.156</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>250</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4177429</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F F </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>01:30:03.428</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>254.272</v>
+      </c>
+      <c r="H15" t="n">
+        <v>156</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1305857</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cedric Palestro (BIKES)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>01:34:01.232</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>213</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3726293</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jonas Sfrt </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>01:41:02.878</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>220</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7964397</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Leandro Cruz</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HTLT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>01:59:19.063</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1096.185</v>
+      </c>
+      <c r="H18" t="n">
+        <v>158</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SpringClassics/SpringClassics.xlsx
+++ b/SpringClassics/SpringClassics.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ride the White Roads race 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Primavera race 1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Primavera race 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobbled Classics race 1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -794,7 +795,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Owen Beckett [R&amp;KBuffaloes]</t>
+          <t>Owen Beckett [R&amp;KJaguars]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1456,7 +1457,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1752,7 +1753,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1930,7 +1931,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1977,7 +1978,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ryan Choi</t>
+          <t>Ryan Choi (Rain City Racing)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2152,7 +2153,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2163,7 +2164,11 @@
           <t>Lucian Stoica</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>58:09.952</t>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Patrick Johansing (SISU)</t>
+          <t>4 Johansing (SISU)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2378,7 +2383,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2569,7 +2574,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2721,7 +2726,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3316,7 +3321,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3747,7 +3752,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nicklas Bekker #SISU#</t>
+          <t>Nicklas Bekker [SISU]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4117,7 +4122,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4245,7 +4250,11 @@
           <t xml:space="preserve">F F </t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>01:30:03.428</t>
@@ -4308,7 +4317,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4372,6 +4381,1247 @@
       </c>
       <c r="I18" t="n">
         <v>1.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>avg_power</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>avg_wkg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2264689</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Evan Bayer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COALITION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>46:17.663</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>319</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4353992</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>* PAC-MAN.*</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>46:18.896</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="H3" t="n">
+        <v>277</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1280650</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">David Finn </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ZSUNR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>46:28.861</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>11.198</v>
+      </c>
+      <c r="H4" t="n">
+        <v>295</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1553452</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tim Neel (watt)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The Watt Squad</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>46:29.022</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>11.359</v>
+      </c>
+      <c r="H5" t="n">
+        <v>243</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5175624</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Alexander Laustsen</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WSport</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>46:31.872</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>14.209</v>
+      </c>
+      <c r="H6" t="n">
+        <v>294</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>954400</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mick Moller [Pow.R]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>POW.&amp;#1071;</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>46:48.825</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>31.162</v>
+      </c>
+      <c r="H7" t="n">
+        <v>304</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7250950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Matthew Gleeson [TNP]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>46:55.942</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>38.279</v>
+      </c>
+      <c r="H8" t="n">
+        <v>255</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3053052</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dave Harcourt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GTC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>47:27.072</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>69.40900000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>365</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6057042</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gero [INOX]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INOX</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>49:16.264</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>178.601</v>
+      </c>
+      <c r="H10" t="n">
+        <v>292</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1038557</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Editor Steve</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HTLT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50:14.110</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>236.447</v>
+      </c>
+      <c r="H11" t="n">
+        <v>270</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12116</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kevin John Boat</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>53:07.702</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>203</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>535397</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A.Roy (OTR)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50:49.975</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>265</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>267262</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bjorn Tore Nergard (V)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vikings</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>52:44.032</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>114.057</v>
+      </c>
+      <c r="H14" t="n">
+        <v>217</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>631162</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Erik  O. Hus&amp;oslash;</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Vikings</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>53:10.691</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>140.716</v>
+      </c>
+      <c r="H15" t="n">
+        <v>244</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2749017</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mike Small7681</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>53:39.305</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>169.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>239</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4753255</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>gregory vandamme [Ghost]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>53:14.145</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>205</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>273047</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Aaron Sch&amp;auml;fer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>53:19.487</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>5.342</v>
+      </c>
+      <c r="H18" t="n">
+        <v>221</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7748162</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cody Normandin</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>56:18.918</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>184.773</v>
+      </c>
+      <c r="H19" t="n">
+        <v>202</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>176437</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mike Brydson</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>56:21.318</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>187.173</v>
+      </c>
+      <c r="H20" t="n">
+        <v>211</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>620051</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jens Christian Bentzon</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DBR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>56:21.348</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>187.203</v>
+      </c>
+      <c r="H21" t="n">
+        <v>233</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5574503</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>David Decherf</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>57:35.313</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>261.168</v>
+      </c>
+      <c r="H22" t="n">
+        <v>260</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>817734</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Luke Austen</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>58:33.133</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>318.988</v>
+      </c>
+      <c r="H23" t="n">
+        <v>216</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5651099</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Emmett Carrier</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>59:08.609</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>354.464</v>
+      </c>
+      <c r="H24" t="n">
+        <v>203</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7799330</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jean-Christophe Hamel</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>59:21.400</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>367.255</v>
+      </c>
+      <c r="H25" t="n">
+        <v>201</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7532389</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ian little</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>59:21.681</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>367.536</v>
+      </c>
+      <c r="H26" t="n">
+        <v>223</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7918519</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sven M</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>01:00:03.657</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>188</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>723456</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T.Vohl</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>01:00:16.022</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>12.365</v>
+      </c>
+      <c r="H28" t="n">
+        <v>170</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6830054</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Michael Eighmey</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>01:00:50.441</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>46.784</v>
+      </c>
+      <c r="H29" t="n">
+        <v>199</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>755268</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ad Paantjens</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>01:04:12.968</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>249.311</v>
+      </c>
+      <c r="H30" t="n">
+        <v>188</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6675111</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jay Locke</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>01:06:25.081</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>381.424</v>
+      </c>
+      <c r="H31" t="n">
+        <v>168</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2264028</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Alvaro Vierna Q</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>01:06:27.032</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>383.375</v>
+      </c>
+      <c r="H32" t="n">
+        <v>158</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5477106</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel aschman </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>01:14:46.451</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>882.794</v>
+      </c>
+      <c r="H33" t="n">
+        <v>146</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
